--- a/Introduction to Excel.xlsx
+++ b/Introduction to Excel.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30006"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="194" documentId="11_0454189CF7C9C261AF790061A5F9C91D624DEE0E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D2C297D-E350-44B2-B37C-EA8B86A3E15E}"/>
+  <xr:revisionPtr revIDLastSave="215" documentId="11_0454189CF7C9C261AF790061A5F9C91D624DEE0E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E2C2950A-CA73-40F0-8E2D-95EEA20A32B3}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Intro " sheetId="1" r:id="rId1"/>
@@ -1983,345 +1983,6 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>#REF!$A$10</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>#REF!</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:strRef>
-              <c:f>#REF!$B$9:$F$9</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>#REF!</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>#REF!$B$10:$F$10</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-9D33-40E6-9D0B-3A0BAFE49B9C}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>#REF!$A$11</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>#REF!</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent2"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:strRef>
-              <c:f>#REF!$B$9:$F$9</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>#REF!</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>#REF!$B$11:$F$11</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-9D33-40E6-9D0B-3A0BAFE49B9C}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="219"/>
-        <c:overlap val="-27"/>
-        <c:axId val="113937416"/>
-        <c:axId val="113955848"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="113937416"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="113955848"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="113955848"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="113937416"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -3432,11 +3093,16 @@
       <a:endParaRPr lang="en-US"/>
     </a:p>
   </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
   <c:extLst/>
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -4888,6 +4554,1819 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst/>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Manufacturing Standards</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="6"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="7"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="8"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="9"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="10"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="11"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="12"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="13"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="14"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="15"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Sum of Fuel_efficiency</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strLit>
+              <c:ptCount val="30"/>
+              <c:pt idx="0">
+                <c:v>Acura</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>Audi</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>BMW</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>Buick</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>Cadillac</c:v>
+              </c:pt>
+              <c:pt idx="5">
+                <c:v>Chevrolet</c:v>
+              </c:pt>
+              <c:pt idx="6">
+                <c:v>Chrysler</c:v>
+              </c:pt>
+              <c:pt idx="7">
+                <c:v>Dodge</c:v>
+              </c:pt>
+              <c:pt idx="8">
+                <c:v>Ford</c:v>
+              </c:pt>
+              <c:pt idx="9">
+                <c:v>Honda</c:v>
+              </c:pt>
+              <c:pt idx="10">
+                <c:v>Hyundai</c:v>
+              </c:pt>
+              <c:pt idx="11">
+                <c:v>Infiniti</c:v>
+              </c:pt>
+              <c:pt idx="12">
+                <c:v>Jaguar</c:v>
+              </c:pt>
+              <c:pt idx="13">
+                <c:v>Jeep</c:v>
+              </c:pt>
+              <c:pt idx="14">
+                <c:v>Lexus</c:v>
+              </c:pt>
+              <c:pt idx="15">
+                <c:v>Lincoln</c:v>
+              </c:pt>
+              <c:pt idx="16">
+                <c:v>Mercedes-B</c:v>
+              </c:pt>
+              <c:pt idx="17">
+                <c:v>Mercury</c:v>
+              </c:pt>
+              <c:pt idx="18">
+                <c:v>Mitsubishi</c:v>
+              </c:pt>
+              <c:pt idx="19">
+                <c:v>Nissan</c:v>
+              </c:pt>
+              <c:pt idx="20">
+                <c:v>Oldsmobile</c:v>
+              </c:pt>
+              <c:pt idx="21">
+                <c:v>Plymouth</c:v>
+              </c:pt>
+              <c:pt idx="22">
+                <c:v>Pontiac</c:v>
+              </c:pt>
+              <c:pt idx="23">
+                <c:v>Porsche</c:v>
+              </c:pt>
+              <c:pt idx="24">
+                <c:v>Saab</c:v>
+              </c:pt>
+              <c:pt idx="25">
+                <c:v>Saturn</c:v>
+              </c:pt>
+              <c:pt idx="26">
+                <c:v>Subaru</c:v>
+              </c:pt>
+              <c:pt idx="27">
+                <c:v>Toyota</c:v>
+              </c:pt>
+              <c:pt idx="28">
+                <c:v>Volkswagen</c:v>
+              </c:pt>
+              <c:pt idx="29">
+                <c:v>Volvo</c:v>
+              </c:pt>
+            </c:strLit>
+          </c:cat>
+          <c:val>
+            <c:numLit>
+              <c:formatCode>General</c:formatCode>
+              <c:ptCount val="30"/>
+              <c:pt idx="0">
+                <c:v>101</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>70</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>75</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>97</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>103</c:v>
+              </c:pt>
+              <c:pt idx="5">
+                <c:v>256</c:v>
+              </c:pt>
+              <c:pt idx="6">
+                <c:v>147</c:v>
+              </c:pt>
+              <c:pt idx="7">
+                <c:v>201</c:v>
+              </c:pt>
+              <c:pt idx="8">
+                <c:v>251</c:v>
+              </c:pt>
+              <c:pt idx="9">
+                <c:v>125</c:v>
+              </c:pt>
+              <c:pt idx="10">
+                <c:v>83</c:v>
+              </c:pt>
+              <c:pt idx="11">
+                <c:v>25</c:v>
+              </c:pt>
+              <c:pt idx="12">
+                <c:v>21</c:v>
+              </c:pt>
+              <c:pt idx="13">
+                <c:v>56</c:v>
+              </c:pt>
+              <c:pt idx="14">
+                <c:v>125</c:v>
+              </c:pt>
+              <c:pt idx="15">
+                <c:v>58</c:v>
+              </c:pt>
+              <c:pt idx="16">
+                <c:v>211</c:v>
+              </c:pt>
+              <c:pt idx="17">
+                <c:v>142</c:v>
+              </c:pt>
+              <c:pt idx="18">
+                <c:v>160</c:v>
+              </c:pt>
+              <c:pt idx="19">
+                <c:v>156</c:v>
+              </c:pt>
+              <c:pt idx="20">
+                <c:v>115</c:v>
+              </c:pt>
+              <c:pt idx="21">
+                <c:v>101</c:v>
+              </c:pt>
+              <c:pt idx="22">
+                <c:v>149</c:v>
+              </c:pt>
+              <c:pt idx="23">
+                <c:v>66</c:v>
+              </c:pt>
+              <c:pt idx="24">
+                <c:v>46</c:v>
+              </c:pt>
+              <c:pt idx="25">
+                <c:v>152</c:v>
+              </c:pt>
+              <c:pt idx="26">
+                <c:v>49</c:v>
+              </c:pt>
+              <c:pt idx="27">
+                <c:v>227</c:v>
+              </c:pt>
+              <c:pt idx="28">
+                <c:v>157</c:v>
+              </c:pt>
+              <c:pt idx="29">
+                <c:v>147</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-86A6-4186-8222-B2DAE83AD488}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Sum of Power_perf_factor</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strLit>
+              <c:ptCount val="30"/>
+              <c:pt idx="0">
+                <c:v>Acura</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>Audi</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>BMW</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>Buick</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>Cadillac</c:v>
+              </c:pt>
+              <c:pt idx="5">
+                <c:v>Chevrolet</c:v>
+              </c:pt>
+              <c:pt idx="6">
+                <c:v>Chrysler</c:v>
+              </c:pt>
+              <c:pt idx="7">
+                <c:v>Dodge</c:v>
+              </c:pt>
+              <c:pt idx="8">
+                <c:v>Ford</c:v>
+              </c:pt>
+              <c:pt idx="9">
+                <c:v>Honda</c:v>
+              </c:pt>
+              <c:pt idx="10">
+                <c:v>Hyundai</c:v>
+              </c:pt>
+              <c:pt idx="11">
+                <c:v>Infiniti</c:v>
+              </c:pt>
+              <c:pt idx="12">
+                <c:v>Jaguar</c:v>
+              </c:pt>
+              <c:pt idx="13">
+                <c:v>Jeep</c:v>
+              </c:pt>
+              <c:pt idx="14">
+                <c:v>Lexus</c:v>
+              </c:pt>
+              <c:pt idx="15">
+                <c:v>Lincoln</c:v>
+              </c:pt>
+              <c:pt idx="16">
+                <c:v>Mercedes-B</c:v>
+              </c:pt>
+              <c:pt idx="17">
+                <c:v>Mercury</c:v>
+              </c:pt>
+              <c:pt idx="18">
+                <c:v>Mitsubishi</c:v>
+              </c:pt>
+              <c:pt idx="19">
+                <c:v>Nissan</c:v>
+              </c:pt>
+              <c:pt idx="20">
+                <c:v>Oldsmobile</c:v>
+              </c:pt>
+              <c:pt idx="21">
+                <c:v>Plymouth</c:v>
+              </c:pt>
+              <c:pt idx="22">
+                <c:v>Pontiac</c:v>
+              </c:pt>
+              <c:pt idx="23">
+                <c:v>Porsche</c:v>
+              </c:pt>
+              <c:pt idx="24">
+                <c:v>Saab</c:v>
+              </c:pt>
+              <c:pt idx="25">
+                <c:v>Saturn</c:v>
+              </c:pt>
+              <c:pt idx="26">
+                <c:v>Subaru</c:v>
+              </c:pt>
+              <c:pt idx="27">
+                <c:v>Toyota</c:v>
+              </c:pt>
+              <c:pt idx="28">
+                <c:v>Volkswagen</c:v>
+              </c:pt>
+              <c:pt idx="29">
+                <c:v>Volvo</c:v>
+              </c:pt>
+            </c:strLit>
+          </c:cat>
+          <c:val>
+            <c:numLit>
+              <c:formatCode>General</c:formatCode>
+              <c:ptCount val="30"/>
+              <c:pt idx="0">
+                <c:v>241.04070651000001</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>281.99960241999997</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>237.06699907000001</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>336.90108791</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>536.23403938000001</c:v>
+              </c:pt>
+              <c:pt idx="5">
+                <c:v>621.37176362000002</c:v>
+              </c:pt>
+              <c:pt idx="6">
+                <c:v>472.05304572</c:v>
+              </c:pt>
+              <c:pt idx="7">
+                <c:v>889.73874860000001</c:v>
+              </c:pt>
+              <c:pt idx="8">
+                <c:v>760.61112547000005</c:v>
+              </c:pt>
+              <c:pt idx="9">
+                <c:v>326.05680439000002</c:v>
+              </c:pt>
+              <c:pt idx="10">
+                <c:v>150.02057773999999</c:v>
+              </c:pt>
+              <c:pt idx="11">
+                <c:v>92.436889230000006</c:v>
+              </c:pt>
+              <c:pt idx="12">
+                <c:v>102.17898479999999</c:v>
+              </c:pt>
+              <c:pt idx="13">
+                <c:v>205.64511665000001</c:v>
+              </c:pt>
+              <c:pt idx="14">
+                <c:v>629.32203270000002</c:v>
+              </c:pt>
+              <c:pt idx="15">
+                <c:v>331.47017049999999</c:v>
+              </c:pt>
+              <c:pt idx="16">
+                <c:v>930.96527724999999</c:v>
+              </c:pt>
+              <c:pt idx="17">
+                <c:v>400.63009020999993</c:v>
+              </c:pt>
+              <c:pt idx="18">
+                <c:v>473.83760617999997</c:v>
+              </c:pt>
+              <c:pt idx="19">
+                <c:v>484.11776019000001</c:v>
+              </c:pt>
+              <c:pt idx="20">
+                <c:v>467.911517</c:v>
+              </c:pt>
+              <c:pt idx="21">
+                <c:v>273.43243784000003</c:v>
+              </c:pt>
+              <c:pt idx="22">
+                <c:v>451.08629697000003</c:v>
+              </c:pt>
+              <c:pt idx="23">
+                <c:v>363.7430157</c:v>
+              </c:pt>
+              <c:pt idx="24">
+                <c:v>149.52682590000001</c:v>
+              </c:pt>
+              <c:pt idx="25">
+                <c:v>241.66724213000001</c:v>
+              </c:pt>
+              <c:pt idx="26">
+                <c:v>134.52885091000002</c:v>
+              </c:pt>
+              <c:pt idx="27">
+                <c:v>593.91332692000003</c:v>
+              </c:pt>
+              <c:pt idx="28">
+                <c:v>300.46734035000003</c:v>
+              </c:pt>
+              <c:pt idx="29">
+                <c:v>461.78135385999997</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-86A6-4186-8222-B2DAE83AD488}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>Count of Vehicle_type</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strLit>
+              <c:ptCount val="30"/>
+              <c:pt idx="0">
+                <c:v>Acura</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>Audi</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>BMW</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>Buick</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>Cadillac</c:v>
+              </c:pt>
+              <c:pt idx="5">
+                <c:v>Chevrolet</c:v>
+              </c:pt>
+              <c:pt idx="6">
+                <c:v>Chrysler</c:v>
+              </c:pt>
+              <c:pt idx="7">
+                <c:v>Dodge</c:v>
+              </c:pt>
+              <c:pt idx="8">
+                <c:v>Ford</c:v>
+              </c:pt>
+              <c:pt idx="9">
+                <c:v>Honda</c:v>
+              </c:pt>
+              <c:pt idx="10">
+                <c:v>Hyundai</c:v>
+              </c:pt>
+              <c:pt idx="11">
+                <c:v>Infiniti</c:v>
+              </c:pt>
+              <c:pt idx="12">
+                <c:v>Jaguar</c:v>
+              </c:pt>
+              <c:pt idx="13">
+                <c:v>Jeep</c:v>
+              </c:pt>
+              <c:pt idx="14">
+                <c:v>Lexus</c:v>
+              </c:pt>
+              <c:pt idx="15">
+                <c:v>Lincoln</c:v>
+              </c:pt>
+              <c:pt idx="16">
+                <c:v>Mercedes-B</c:v>
+              </c:pt>
+              <c:pt idx="17">
+                <c:v>Mercury</c:v>
+              </c:pt>
+              <c:pt idx="18">
+                <c:v>Mitsubishi</c:v>
+              </c:pt>
+              <c:pt idx="19">
+                <c:v>Nissan</c:v>
+              </c:pt>
+              <c:pt idx="20">
+                <c:v>Oldsmobile</c:v>
+              </c:pt>
+              <c:pt idx="21">
+                <c:v>Plymouth</c:v>
+              </c:pt>
+              <c:pt idx="22">
+                <c:v>Pontiac</c:v>
+              </c:pt>
+              <c:pt idx="23">
+                <c:v>Porsche</c:v>
+              </c:pt>
+              <c:pt idx="24">
+                <c:v>Saab</c:v>
+              </c:pt>
+              <c:pt idx="25">
+                <c:v>Saturn</c:v>
+              </c:pt>
+              <c:pt idx="26">
+                <c:v>Subaru</c:v>
+              </c:pt>
+              <c:pt idx="27">
+                <c:v>Toyota</c:v>
+              </c:pt>
+              <c:pt idx="28">
+                <c:v>Volkswagen</c:v>
+              </c:pt>
+              <c:pt idx="29">
+                <c:v>Volvo</c:v>
+              </c:pt>
+            </c:strLit>
+          </c:cat>
+          <c:val>
+            <c:numLit>
+              <c:formatCode>General</c:formatCode>
+              <c:ptCount val="30"/>
+              <c:pt idx="0">
+                <c:v>4</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>3</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>3</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>4</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>5</c:v>
+              </c:pt>
+              <c:pt idx="5">
+                <c:v>9</c:v>
+              </c:pt>
+              <c:pt idx="6">
+                <c:v>7</c:v>
+              </c:pt>
+              <c:pt idx="7">
+                <c:v>11</c:v>
+              </c:pt>
+              <c:pt idx="8">
+                <c:v>11</c:v>
+              </c:pt>
+              <c:pt idx="9">
+                <c:v>5</c:v>
+              </c:pt>
+              <c:pt idx="10">
+                <c:v>3</c:v>
+              </c:pt>
+              <c:pt idx="11">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="12">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="13">
+                <c:v>3</c:v>
+              </c:pt>
+              <c:pt idx="14">
+                <c:v>6</c:v>
+              </c:pt>
+              <c:pt idx="15">
+                <c:v>3</c:v>
+              </c:pt>
+              <c:pt idx="16">
+                <c:v>9</c:v>
+              </c:pt>
+              <c:pt idx="17">
+                <c:v>6</c:v>
+              </c:pt>
+              <c:pt idx="18">
+                <c:v>7</c:v>
+              </c:pt>
+              <c:pt idx="19">
+                <c:v>7</c:v>
+              </c:pt>
+              <c:pt idx="20">
+                <c:v>6</c:v>
+              </c:pt>
+              <c:pt idx="21">
+                <c:v>4</c:v>
+              </c:pt>
+              <c:pt idx="22">
+                <c:v>6</c:v>
+              </c:pt>
+              <c:pt idx="23">
+                <c:v>3</c:v>
+              </c:pt>
+              <c:pt idx="24">
+                <c:v>2</c:v>
+              </c:pt>
+              <c:pt idx="25">
+                <c:v>5</c:v>
+              </c:pt>
+              <c:pt idx="26">
+                <c:v>2</c:v>
+              </c:pt>
+              <c:pt idx="27">
+                <c:v>9</c:v>
+              </c:pt>
+              <c:pt idx="28">
+                <c:v>6</c:v>
+              </c:pt>
+              <c:pt idx="29">
+                <c:v>6</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-86A6-4186-8222-B2DAE83AD488}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1354159623"/>
+        <c:axId val="927859207"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1354159623"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="927859207"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="927859207"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1354159623"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -5598,509 +7077,6 @@
 </file>
 
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -6619,7 +7595,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -7124,20 +8100,523 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>276225</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:colOff>590550</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>581025</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -7166,23 +8645,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>333375</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="6" name="Chart 5">
+        <xdr:cNvPr id="7" name="Chart 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{30714CFF-63D1-4A47-8A90-5FB65864FA05}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A9728CE6-89E2-4993-A565-192AF7C56288}"/>
             </a:ext>
             <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
               <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{4F6BB9D9-F941-421F-9E5B-3C4386274298}"/>
@@ -7207,26 +8686,26 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>295275</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>600075</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>333375</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="7" name="Chart 6">
+        <xdr:cNvPr id="8" name="Chart 8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A9728CE6-89E2-4993-A565-192AF7C56288}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E6826541-3346-4CC2-8FBF-9683A58A6ADF}"/>
             </a:ext>
             <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{30714CFF-63D1-4A47-8A90-5FB65864FA05}"/>
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{A9728CE6-89E2-4993-A565-192AF7C56288}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7248,26 +8727,26 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>514350</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>323850</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="8" name="Chart 8">
+        <xdr:cNvPr id="3" name="Chart 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E6826541-3346-4CC2-8FBF-9683A58A6ADF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{88197EB9-C524-4E16-A2DD-D98FFA7ACA14}"/>
             </a:ext>
             <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{A9728CE6-89E2-4993-A565-192AF7C56288}"/>
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{E6826541-3346-4CC2-8FBF-9683A58A6ADF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
